--- a/Result/profitability/2537.xlsx
+++ b/Result/profitability/2537.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12875</v>
+        <v>0.12125</v>
       </c>
       <c r="N2" t="n">
-        <v>35.74375</v>
+        <v>35.52875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.11375</v>
+        <v>0.05875</v>
       </c>
       <c r="N3" t="n">
-        <v>43.07375</v>
+        <v>41.85875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06125000000000001</v>
+        <v>0.03500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>41.655</v>
+        <v>40.33125</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01250000000000001</v>
+        <v>0.02375000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>36.24375</v>
+        <v>36.1075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01625000000000001</v>
+        <v>0.02500000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>34.87375</v>
+        <v>34.77375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03500000000000002</v>
+        <v>0.03250000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>32.735</v>
+        <v>34.17375000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05000000000000002</v>
+        <v>0.002500000000000013</v>
       </c>
       <c r="N8" t="n">
-        <v>32.09</v>
+        <v>33.09625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2537</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>252</v>
+      </c>
+      <c r="D75" t="n">
+        <v>178</v>
+      </c>
+      <c r="E75" t="n">
+        <v>74</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.13875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3765201122544435</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0357142857142857</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
